--- a/MAJSushiConfig/ig/StructureDefinition-fr-device-request-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-device-request-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-request-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-request-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -461,7 +461,7 @@
     <t>notCovered</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-not-covered-extension|0.1.0}
 </t>
   </si>
   <si>
@@ -1424,7 +1424,7 @@
     <t>DeviceRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1525,7 +1525,7 @@
     <t>DeviceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
+    <t xml:space="preserve">Reference(Observation|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-condition-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-prevention-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-ald-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-observation-work-related-accident-document|0.1.0)
 </t>
   </si>
   <si>
